--- a/data.xlsx
+++ b/data.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\TPusb03\Transfer\Tableau_Data\職域開發專案\DAYLY\台積電\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06C0FE8-4E2A-4487-8190-DA033A31D593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A598252F-84E5-4133-9C16-4BD5F6270E7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="各管道每日加入人數" sheetId="11" r:id="rId1"/>
     <sheet name="Data_回覆時程" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_Data_回覆時程AO1" hidden="1">Data_回覆時程!$A:$O</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Data_回覆時程!$A$1:$S$1</definedName>
+    <definedName name="_xlcn.WorksheetConnection_Data_回覆時程AO" hidden="1">Data_回覆時程!$A:$O</definedName>
     <definedName name="外部資料_1" localSheetId="0" hidden="1">各管道每日加入人數!$A$2:$E$191</definedName>
     <definedName name="外部資料_2" localSheetId="0" hidden="1">各管道每日加入人數!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="6" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -70,7 +71,7 @@
       </ext>
     </extLst>
   </connection>
-  <connection id="3" xr16:uid="{00000000-0015-0000-FFFF-FFFF02000000}" keepAlive="1" name="ThisWorkbookDataModel" description="資料模型" type="5" refreshedVersion="6" minRefreshableVersion="5" background="1">
+  <connection id="3" xr16:uid="{00000000-0015-0000-FFFF-FFFF02000000}" keepAlive="1" name="ThisWorkbookDataModel" description="資料模型" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
     <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
     <olapPr sendLocale="1" rowDrillCount="1000"/>
     <extLst>
@@ -83,7 +84,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="範圍" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Data_回覆時程AO1"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Data_回覆時程AO"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -108,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4177" uniqueCount="1916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4183" uniqueCount="1916">
   <si>
     <t>Ub51cd98fbce5a53f1da4a945bdf98593</t>
   </si>
@@ -5961,7 +5962,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5995,17 +5996,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6013,12 +6011,1906 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="82">
+  <dxfs count="232">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微軟正黑體"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -7090,17 +8982,18 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="陳奕廷 Yi Ting Chen - KGIL" refreshedDate="46196.612931249998" backgroundQuery="1" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{00000000-000A-0000-FFFF-FFFF03000000}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="陳奕廷-職域開發專案" refreshedDate="46196.694600462964" backgroundQuery="1" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{00000000-000A-0000-FFFF-FFFF03000000}">
   <cacheSource type="external" connectionId="3"/>
   <cacheFields count="5">
     <cacheField name="[範圍].[AREA].[AREA]" caption="AREA" numFmtId="0" hierarchy="10" level="1">
-      <sharedItems count="27">
+      <sharedItems count="30">
         <s v="AP5B"/>
         <s v="AP6A"/>
         <s v="AP6B"/>
         <s v="AP7"/>
         <s v="F15A"/>
         <s v="F15B"/>
+        <s v="其他廠區(台中地區)"/>
         <s v="AP8"/>
         <s v="F14P1"/>
         <s v="F14P3"/>
@@ -7109,6 +9002,7 @@
         <s v="F18A"/>
         <s v="F18B"/>
         <s v="F6"/>
+        <s v="其他廠區(台南地區)"/>
         <s v="AP3龍潭廠"/>
         <s v="F12P1"/>
         <s v="F12P4"/>
@@ -7120,6 +9014,7 @@
         <s v="F3"/>
         <s v="F7"/>
         <s v="F8"/>
+        <s v="其他廠區(新竹地區)"/>
         <s v="F18P8"/>
         <s v="F22"/>
       </sharedItems>
@@ -7277,38 +9172,41 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="樞紐分析表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption=" " updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" mergeItem="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0" rowHeaderCaption="廠區">
-  <location ref="A228:E260" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="樞紐分析表1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption=" " updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" mergeItem="1" createdVersion="6" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0" rowHeaderCaption="廠區">
+  <location ref="A228:E263" firstHeaderRow="1" firstDataRow="2" firstDataCol="3"/>
   <pivotFields count="5">
     <pivotField name="廠區" axis="axisRow" compact="0" allDrilled="1" outline="0" showAll="0" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="27">
-        <item s="1" x="0"/>
-        <item s="1" x="1"/>
-        <item s="1" x="2"/>
-        <item s="1" x="3"/>
-        <item s="1" x="4"/>
-        <item s="1" x="5"/>
-        <item s="1" x="6"/>
-        <item s="1" x="7"/>
-        <item s="1" x="8"/>
-        <item s="1" x="9"/>
-        <item s="1" x="10"/>
-        <item s="1" x="11"/>
-        <item s="1" x="12"/>
-        <item s="1" x="13"/>
-        <item s="1" x="14"/>
-        <item s="1" x="15"/>
-        <item s="1" x="16"/>
-        <item s="1" x="17"/>
-        <item s="1" x="18"/>
-        <item s="1" x="19"/>
-        <item s="1" x="20"/>
-        <item s="1" x="21"/>
-        <item s="1" x="22"/>
-        <item s="1" x="23"/>
-        <item s="1" x="24"/>
-        <item s="1" x="25"/>
-        <item s="1" x="26"/>
+      <items count="30">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
       </items>
       <autoSortScope>
         <pivotArea dataOnly="0" outline="0" fieldPosition="0">
@@ -7374,10 +9272,10 @@
     <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
+        <item s="1" x="0"/>
+        <item s="1" x="1"/>
+        <item s="1" x="2"/>
+        <item s="1" x="3"/>
       </items>
     </pivotField>
   </pivotFields>
@@ -7386,7 +9284,7 @@
     <field x="0"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="31">
+  <rowItems count="34">
     <i>
       <x/>
       <x v="4"/>
@@ -7415,97 +9313,109 @@
       <x v="1"/>
       <x v="1"/>
     </i>
+    <i r="1">
+      <x v="6"/>
+      <x v="1"/>
+    </i>
     <i>
       <x v="1"/>
-      <x v="6"/>
+      <x v="7"/>
       <x v="7"/>
     </i>
     <i r="1">
-      <x v="11"/>
+      <x v="12"/>
       <x v="13"/>
     </i>
     <i r="1">
-      <x v="9"/>
+      <x v="10"/>
       <x v="10"/>
     </i>
     <i r="1">
-      <x v="12"/>
+      <x v="13"/>
       <x v="14"/>
     </i>
     <i r="1">
-      <x v="10"/>
+      <x v="11"/>
       <x v="12"/>
     </i>
     <i r="2">
       <x v="11"/>
     </i>
     <i r="1">
-      <x v="7"/>
+      <x v="8"/>
       <x v="8"/>
     </i>
     <i r="1">
-      <x v="8"/>
+      <x v="9"/>
       <x v="9"/>
     </i>
     <i r="1">
-      <x v="13"/>
+      <x v="14"/>
+      <x v="8"/>
+    </i>
+    <i r="1">
+      <x v="15"/>
       <x v="8"/>
     </i>
     <i>
       <x v="2"/>
-      <x v="21"/>
+      <x v="23"/>
       <x v="21"/>
     </i>
     <i r="1">
-      <x v="19"/>
+      <x v="21"/>
       <x v="19"/>
     </i>
     <i r="1">
-      <x v="20"/>
+      <x v="22"/>
       <x v="20"/>
     </i>
     <i r="1">
+      <x v="20"/>
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="17"/>
+      <x v="16"/>
+    </i>
+    <i r="1">
+      <x v="19"/>
+      <x v="18"/>
+    </i>
+    <i r="1">
+      <x v="16"/>
       <x v="15"/>
-      <x v="16"/>
     </i>
     <i r="1">
       <x v="18"/>
       <x v="17"/>
     </i>
     <i r="1">
-      <x v="17"/>
-      <x v="18"/>
-    </i>
-    <i r="1">
-      <x v="14"/>
-      <x v="15"/>
-    </i>
-    <i r="1">
-      <x v="16"/>
-      <x v="17"/>
-    </i>
-    <i r="1">
-      <x v="22"/>
+      <x v="24"/>
       <x v="22"/>
     </i>
     <i r="1">
-      <x v="23"/>
+      <x v="25"/>
       <x v="16"/>
     </i>
     <i r="1">
-      <x v="24"/>
+      <x v="26"/>
       <x v="24"/>
     </i>
     <i r="2">
       <x v="23"/>
     </i>
+    <i r="1">
+      <x v="27"/>
+      <x v="20"/>
+    </i>
     <i>
       <x v="3"/>
-      <x v="26"/>
+      <x v="29"/>
       <x v="26"/>
     </i>
     <i r="1">
-      <x v="25"/>
+      <x v="28"/>
       <x v="25"/>
     </i>
     <i t="grand">
@@ -7534,7 +9444,7 @@
     <dataField name="三天內回覆" fld="3" baseField="2" baseItem="2"/>
   </dataFields>
   <formats count="75">
-    <format dxfId="81">
+    <format dxfId="231">
       <pivotArea outline="0" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -7545,24 +9455,24 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="80">
+    <format dxfId="230">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="79">
+    <format dxfId="229">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="228">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="77">
+    <format dxfId="227">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="14"/>
+            <x v="16"/>
           </reference>
           <reference field="2" count="1">
             <x v="15"/>
@@ -7570,7 +9480,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="76">
+    <format dxfId="226">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7582,7 +9492,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="75">
+    <format dxfId="225">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7594,7 +9504,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="74">
+    <format dxfId="224">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7606,7 +9516,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="223">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7618,11 +9528,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="222">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="6"/>
+            <x v="7"/>
           </reference>
           <reference field="2" count="1">
             <x v="7"/>
@@ -7630,11 +9540,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="221">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="15"/>
+            <x v="17"/>
           </reference>
           <reference field="2" count="1">
             <x v="16"/>
@@ -7642,31 +9552,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1" selected="0">
-            <x v="16"/>
-          </reference>
-          <reference field="2" count="1">
-            <x v="17"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="69">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1" selected="0">
-            <x v="17"/>
-          </reference>
-          <reference field="2" count="1">
-            <x v="18"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="68">
+    <format dxfId="220">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7678,11 +9564,35 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="67">
+    <format dxfId="219">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
             <x v="19"/>
+          </reference>
+          <reference field="2" count="1">
+            <x v="18"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="218">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="2" count="1">
+            <x v="17"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="217">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="21"/>
           </reference>
           <reference field="2" count="1">
             <x v="19"/>
@@ -7690,11 +9600,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="216">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="7"/>
+            <x v="8"/>
           </reference>
           <reference field="2" count="1">
             <x v="8"/>
@@ -7702,11 +9612,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="65">
+    <format dxfId="215">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="8"/>
+            <x v="9"/>
           </reference>
           <reference field="2" count="1">
             <x v="9"/>
@@ -7714,11 +9624,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="214">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="9"/>
+            <x v="10"/>
           </reference>
           <reference field="2" count="1">
             <x v="10"/>
@@ -7726,11 +9636,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="213">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="10"/>
+            <x v="11"/>
           </reference>
           <reference field="2" count="2">
             <x v="11"/>
@@ -7739,7 +9649,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="62">
+    <format dxfId="212">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7751,7 +9661,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="211">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7764,11 +9674,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="210">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="11"/>
+            <x v="12"/>
           </reference>
           <reference field="2" count="1">
             <x v="13"/>
@@ -7776,11 +9686,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
+    <format dxfId="209">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="12"/>
+            <x v="13"/>
           </reference>
           <reference field="2" count="1">
             <x v="14"/>
@@ -7788,11 +9698,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="58">
+    <format dxfId="208">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="25"/>
+            <x v="28"/>
           </reference>
           <reference field="2" count="1">
             <x v="25"/>
@@ -7800,11 +9710,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="57">
+    <format dxfId="207">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="20"/>
+            <x v="22"/>
           </reference>
           <reference field="2" count="1">
             <x v="20"/>
@@ -7812,11 +9722,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="206">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="21"/>
+            <x v="23"/>
           </reference>
           <reference field="2" count="1">
             <x v="21"/>
@@ -7824,11 +9734,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="55">
+    <format dxfId="205">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="26"/>
+            <x v="29"/>
           </reference>
           <reference field="2" count="1">
             <x v="26"/>
@@ -7836,11 +9746,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="54">
+    <format dxfId="204">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="22"/>
+            <x v="24"/>
           </reference>
           <reference field="2" count="1">
             <x v="22"/>
@@ -7848,11 +9758,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="53">
+    <format dxfId="203">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="13"/>
+            <x v="14"/>
           </reference>
           <reference field="2" count="1">
             <x v="8"/>
@@ -7860,11 +9770,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="52">
+    <format dxfId="202">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="23"/>
+            <x v="25"/>
           </reference>
           <reference field="2" count="1">
             <x v="16"/>
@@ -7872,11 +9782,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="51">
+    <format dxfId="201">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="24"/>
+            <x v="26"/>
           </reference>
           <reference field="2" count="1">
             <x v="24"/>
@@ -7884,7 +9794,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="50">
+    <format dxfId="200">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -7893,42 +9803,42 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="49">
+    <format dxfId="199">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="198">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="197">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="196">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="45">
+    <format dxfId="195">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="194">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="193">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="192">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="191">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="190">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="14"/>
+            <x v="16"/>
           </reference>
           <reference field="2" count="1">
             <x v="15"/>
@@ -7936,7 +9846,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
+    <format dxfId="189">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7948,7 +9858,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="188">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7960,7 +9870,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="187">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7972,7 +9882,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="36">
+    <format dxfId="186">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -7984,11 +9894,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="35">
+    <format dxfId="185">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="6"/>
+            <x v="7"/>
           </reference>
           <reference field="2" count="1">
             <x v="7"/>
@@ -7996,11 +9906,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="34">
+    <format dxfId="184">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="15"/>
+            <x v="17"/>
           </reference>
           <reference field="2" count="1">
             <x v="16"/>
@@ -8008,31 +9918,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="33">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1" selected="0">
-            <x v="16"/>
-          </reference>
-          <reference field="2" count="1">
-            <x v="17"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="1" selected="0">
-            <x v="17"/>
-          </reference>
-          <reference field="2" count="1">
-            <x v="18"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="31">
+    <format dxfId="183">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -8044,11 +9930,35 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="182">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
             <x v="19"/>
+          </reference>
+          <reference field="2" count="1">
+            <x v="18"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="181">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="20"/>
+          </reference>
+          <reference field="2" count="1">
+            <x v="17"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="180">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="1" selected="0">
+            <x v="21"/>
           </reference>
           <reference field="2" count="1">
             <x v="19"/>
@@ -8056,11 +9966,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="179">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="7"/>
+            <x v="8"/>
           </reference>
           <reference field="2" count="1">
             <x v="8"/>
@@ -8068,11 +9978,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="178">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="8"/>
+            <x v="9"/>
           </reference>
           <reference field="2" count="1">
             <x v="9"/>
@@ -8080,11 +9990,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="177">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="9"/>
+            <x v="10"/>
           </reference>
           <reference field="2" count="1">
             <x v="10"/>
@@ -8092,11 +10002,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="26">
+    <format dxfId="176">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="10"/>
+            <x v="11"/>
           </reference>
           <reference field="2" count="2">
             <x v="11"/>
@@ -8105,7 +10015,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="175">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -8117,7 +10027,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="174">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -8130,11 +10040,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="173">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="11"/>
+            <x v="12"/>
           </reference>
           <reference field="2" count="1">
             <x v="13"/>
@@ -8142,11 +10052,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="172">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="12"/>
+            <x v="13"/>
           </reference>
           <reference field="2" count="1">
             <x v="14"/>
@@ -8154,11 +10064,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="171">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="25"/>
+            <x v="28"/>
           </reference>
           <reference field="2" count="1">
             <x v="25"/>
@@ -8166,11 +10076,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="170">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="20"/>
+            <x v="22"/>
           </reference>
           <reference field="2" count="1">
             <x v="20"/>
@@ -8178,11 +10088,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="169">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="21"/>
+            <x v="23"/>
           </reference>
           <reference field="2" count="1">
             <x v="21"/>
@@ -8190,11 +10100,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="168">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="26"/>
+            <x v="29"/>
           </reference>
           <reference field="2" count="1">
             <x v="26"/>
@@ -8202,11 +10112,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="167">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="22"/>
+            <x v="24"/>
           </reference>
           <reference field="2" count="1">
             <x v="22"/>
@@ -8214,11 +10124,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="166">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="13"/>
+            <x v="14"/>
           </reference>
           <reference field="2" count="1">
             <x v="8"/>
@@ -8226,11 +10136,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="165">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="23"/>
+            <x v="25"/>
           </reference>
           <reference field="2" count="1">
             <x v="16"/>
@@ -8238,11 +10148,11 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="164">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
-            <x v="24"/>
+            <x v="26"/>
           </reference>
           <reference field="2" count="1">
             <x v="24"/>
@@ -8250,7 +10160,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="163">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -8260,34 +10170,34 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="162">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
-            <x v="10"/>
+            <x v="11"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="161">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="0" count="1">
-            <x v="10"/>
+            <x v="11"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="160">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="159">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="1"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="158">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="2"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="157">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="2">
@@ -8374,17 +10284,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="加入人數" displayName="加入人數" ref="A2:E191" tableType="queryTable" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="加入人數" displayName="加入人數" ref="A2:E191" tableType="queryTable" totalsRowShown="0" headerRowDxfId="156" dataDxfId="155">
   <autoFilter ref="A2:E191" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E191">
     <sortCondition ref="A10:A52"/>
   </sortState>
   <tableColumns count="5">
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" uniqueName="6" name="加入LINE OA日期" queryTableFieldId="1" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" uniqueName="7" name="由HR公告加入" queryTableFieldId="2" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" uniqueName="8" name="由服務小卡加入" queryTableFieldId="3" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" uniqueName="9" name="由好友推薦加入" queryTableFieldId="4" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" uniqueName="10" name="總加入人數" queryTableFieldId="5" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" uniqueName="6" name="加入LINE OA日期" queryTableFieldId="1" dataDxfId="154"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" uniqueName="7" name="由HR公告加入" queryTableFieldId="2" dataDxfId="153"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" uniqueName="8" name="由服務小卡加入" queryTableFieldId="3" dataDxfId="152"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" uniqueName="9" name="由好友推薦加入" queryTableFieldId="4" dataDxfId="151"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" uniqueName="10" name="總加入人數" queryTableFieldId="5" dataDxfId="150"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8653,25 +10563,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P263"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:P264"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.625" style="2" customWidth="1"/>
+    <col min="3" max="5" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15" style="2" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="16" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>988</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>98</v>
       </c>
@@ -8688,7 +10598,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>45993</v>
       </c>
@@ -8705,7 +10615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>45996</v>
       </c>
@@ -8722,7 +10632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>45999</v>
       </c>
@@ -8739,7 +10649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>46000</v>
       </c>
@@ -8756,7 +10666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>46002</v>
       </c>
@@ -8773,7 +10683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>46006</v>
       </c>
@@ -8801,7 +10711,7 @@
       <c r="O8"/>
       <c r="P8"/>
     </row>
-    <row r="9" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>46007</v>
       </c>
@@ -8829,7 +10739,7 @@
       <c r="O9"/>
       <c r="P9"/>
     </row>
-    <row r="10" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>46008</v>
       </c>
@@ -8857,7 +10767,7 @@
       <c r="O10"/>
       <c r="P10"/>
     </row>
-    <row r="11" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>46009</v>
       </c>
@@ -8885,7 +10795,7 @@
       <c r="O11"/>
       <c r="P11"/>
     </row>
-    <row r="12" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>46010</v>
       </c>
@@ -8913,7 +10823,7 @@
       <c r="O12"/>
       <c r="P12"/>
     </row>
-    <row r="13" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>46011</v>
       </c>
@@ -8941,7 +10851,7 @@
       <c r="O13"/>
       <c r="P13"/>
     </row>
-    <row r="14" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>46012</v>
       </c>
@@ -8969,7 +10879,7 @@
       <c r="O14"/>
       <c r="P14"/>
     </row>
-    <row r="15" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>46013</v>
       </c>
@@ -8997,7 +10907,7 @@
       <c r="O15"/>
       <c r="P15"/>
     </row>
-    <row r="16" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>46014</v>
       </c>
@@ -9025,7 +10935,7 @@
       <c r="O16"/>
       <c r="P16"/>
     </row>
-    <row r="17" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>46015</v>
       </c>
@@ -9053,7 +10963,7 @@
       <c r="O17"/>
       <c r="P17"/>
     </row>
-    <row r="18" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>46016</v>
       </c>
@@ -9081,7 +10991,7 @@
       <c r="O18"/>
       <c r="P18"/>
     </row>
-    <row r="19" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>46017</v>
       </c>
@@ -9109,7 +11019,7 @@
       <c r="O19"/>
       <c r="P19"/>
     </row>
-    <row r="20" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>46018</v>
       </c>
@@ -9137,7 +11047,7 @@
       <c r="O20"/>
       <c r="P20"/>
     </row>
-    <row r="21" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>46019</v>
       </c>
@@ -9165,7 +11075,7 @@
       <c r="O21"/>
       <c r="P21"/>
     </row>
-    <row r="22" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>46020</v>
       </c>
@@ -9193,7 +11103,7 @@
       <c r="O22"/>
       <c r="P22"/>
     </row>
-    <row r="23" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>46021</v>
       </c>
@@ -9221,7 +11131,7 @@
       <c r="O23"/>
       <c r="P23"/>
     </row>
-    <row r="24" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>46022</v>
       </c>
@@ -9249,7 +11159,7 @@
       <c r="O24"/>
       <c r="P24"/>
     </row>
-    <row r="25" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>46023</v>
       </c>
@@ -9277,7 +11187,7 @@
       <c r="O25"/>
       <c r="P25"/>
     </row>
-    <row r="26" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>46024</v>
       </c>
@@ -9305,7 +11215,7 @@
       <c r="O26"/>
       <c r="P26"/>
     </row>
-    <row r="27" spans="1:16" ht="17" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:16" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>46025</v>
       </c>
@@ -9333,7 +11243,7 @@
       <c r="O27"/>
       <c r="P27"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>46026</v>
       </c>
@@ -9350,7 +11260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="7">
         <v>46027</v>
       </c>
@@ -9367,7 +11277,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="7">
         <v>46028</v>
       </c>
@@ -9384,7 +11294,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="7">
         <v>46029</v>
       </c>
@@ -9401,7 +11311,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="7">
         <v>46030</v>
       </c>
@@ -9418,7 +11328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="7">
         <v>46031</v>
       </c>
@@ -9435,7 +11345,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="7">
         <v>46032</v>
       </c>
@@ -9452,7 +11362,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="7">
         <v>46033</v>
       </c>
@@ -9469,7 +11379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="7">
         <v>46034</v>
       </c>
@@ -9486,7 +11396,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
         <v>46035</v>
       </c>
@@ -9503,7 +11413,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="7">
         <v>46036</v>
       </c>
@@ -9520,7 +11430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="7">
         <v>46037</v>
       </c>
@@ -9537,7 +11447,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="7">
         <v>46038</v>
       </c>
@@ -9554,7 +11464,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="7">
         <v>46039</v>
       </c>
@@ -9571,7 +11481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="7">
         <v>46040</v>
       </c>
@@ -9588,7 +11498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="7">
         <v>46041</v>
       </c>
@@ -9605,7 +11515,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="7">
         <v>46042</v>
       </c>
@@ -9622,7 +11532,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="7">
         <v>46043</v>
       </c>
@@ -9639,7 +11549,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="7">
         <v>46044</v>
       </c>
@@ -9656,7 +11566,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="7">
         <v>46045</v>
       </c>
@@ -9673,7 +11583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="7">
         <v>46046</v>
       </c>
@@ -9690,7 +11600,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="7">
         <v>46047</v>
       </c>
@@ -9707,7 +11617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="7">
         <v>46048</v>
       </c>
@@ -9724,7 +11634,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="7">
         <v>46049</v>
       </c>
@@ -9741,7 +11651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="7">
         <v>46050</v>
       </c>
@@ -9758,7 +11668,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="7">
         <v>46051</v>
       </c>
@@ -9775,7 +11685,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>46052</v>
       </c>
@@ -9792,7 +11702,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="7">
         <v>46054</v>
       </c>
@@ -9809,7 +11719,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="7">
         <v>46055</v>
       </c>
@@ -9826,7 +11736,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="7">
         <v>46056</v>
       </c>
@@ -9843,7 +11753,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="7">
         <v>46057</v>
       </c>
@@ -9860,7 +11770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="7">
         <v>46058</v>
       </c>
@@ -9877,7 +11787,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="7">
         <v>46059</v>
       </c>
@@ -9894,7 +11804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="7">
         <v>46060</v>
       </c>
@@ -9911,7 +11821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>46061</v>
       </c>
@@ -9928,7 +11838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="7">
         <v>46062</v>
       </c>
@@ -9945,7 +11855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="7">
         <v>46063</v>
       </c>
@@ -9962,7 +11872,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="7">
         <v>46064</v>
       </c>
@@ -9979,7 +11889,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="7">
         <v>46065</v>
       </c>
@@ -9996,7 +11906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="7">
         <v>46066</v>
       </c>
@@ -10013,7 +11923,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="7">
         <v>46067</v>
       </c>
@@ -10030,7 +11940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="7">
         <v>46068</v>
       </c>
@@ -10047,7 +11957,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="7">
         <v>46069</v>
       </c>
@@ -10064,7 +11974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="7">
         <v>46071</v>
       </c>
@@ -10081,7 +11991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="7">
         <v>46072</v>
       </c>
@@ -10098,7 +12008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="7">
         <v>46073</v>
       </c>
@@ -10115,7 +12025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="7">
         <v>46074</v>
       </c>
@@ -10132,7 +12042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="7">
         <v>46075</v>
       </c>
@@ -10149,7 +12059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="7">
         <v>46076</v>
       </c>
@@ -10166,7 +12076,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="7">
         <v>46077</v>
       </c>
@@ -10183,7 +12093,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="7">
         <v>46078</v>
       </c>
@@ -10200,7 +12110,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="7">
         <v>46079</v>
       </c>
@@ -10217,7 +12127,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="7">
         <v>46080</v>
       </c>
@@ -10234,7 +12144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="7">
         <v>46081</v>
       </c>
@@ -10251,7 +12161,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="7">
         <v>46082</v>
       </c>
@@ -10268,7 +12178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="7">
         <v>46083</v>
       </c>
@@ -10285,7 +12195,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="7">
         <v>46084</v>
       </c>
@@ -10302,7 +12212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="7">
         <v>46085</v>
       </c>
@@ -10319,7 +12229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="7">
         <v>46086</v>
       </c>
@@ -10336,7 +12246,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="7">
         <v>46087</v>
       </c>
@@ -10353,7 +12263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="7">
         <v>46088</v>
       </c>
@@ -10370,7 +12280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="7">
         <v>46089</v>
       </c>
@@ -10387,7 +12297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="7">
         <v>46090</v>
       </c>
@@ -10404,7 +12314,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="7">
         <v>46091</v>
       </c>
@@ -10421,7 +12331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="7">
         <v>46092</v>
       </c>
@@ -10438,7 +12348,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="7">
         <v>46093</v>
       </c>
@@ -10455,7 +12365,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="7">
         <v>46094</v>
       </c>
@@ -10472,7 +12382,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="7">
         <v>46095</v>
       </c>
@@ -10489,7 +12399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="7">
         <v>46096</v>
       </c>
@@ -10506,7 +12416,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="7">
         <v>46097</v>
       </c>
@@ -10523,7 +12433,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="7">
         <v>46098</v>
       </c>
@@ -10540,7 +12450,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="7">
         <v>46099</v>
       </c>
@@ -10557,7 +12467,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="7">
         <v>46100</v>
       </c>
@@ -10574,7 +12484,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="7">
         <v>46101</v>
       </c>
@@ -10591,7 +12501,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="7">
         <v>46102</v>
       </c>
@@ -10608,7 +12518,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="7">
         <v>46103</v>
       </c>
@@ -10625,7 +12535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="7">
         <v>46104</v>
       </c>
@@ -10642,7 +12552,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="7">
         <v>46105</v>
       </c>
@@ -10659,7 +12569,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="7">
         <v>46106</v>
       </c>
@@ -10676,7 +12586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="7">
         <v>46107</v>
       </c>
@@ -10693,7 +12603,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="7">
         <v>46108</v>
       </c>
@@ -10710,7 +12620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="7">
         <v>46110</v>
       </c>
@@ -10727,7 +12637,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="7">
         <v>46111</v>
       </c>
@@ -10744,7 +12654,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="7">
         <v>46112</v>
       </c>
@@ -10761,7 +12671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="7">
         <v>46113</v>
       </c>
@@ -10778,7 +12688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="7">
         <v>46114</v>
       </c>
@@ -10795,7 +12705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="7">
         <v>46115</v>
       </c>
@@ -10812,7 +12722,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="7">
         <v>46116</v>
       </c>
@@ -10829,7 +12739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="7">
         <v>46117</v>
       </c>
@@ -10846,7 +12756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="7">
         <v>46118</v>
       </c>
@@ -10863,7 +12773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="7">
         <v>46119</v>
       </c>
@@ -10880,7 +12790,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="7">
         <v>46120</v>
       </c>
@@ -10897,7 +12807,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="7">
         <v>46121</v>
       </c>
@@ -10914,7 +12824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="7">
         <v>46122</v>
       </c>
@@ -10931,7 +12841,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="7">
         <v>46123</v>
       </c>
@@ -10948,7 +12858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="7">
         <v>46125</v>
       </c>
@@ -10965,7 +12875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="7">
         <v>46126</v>
       </c>
@@ -10982,7 +12892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="7">
         <v>46127</v>
       </c>
@@ -10999,7 +12909,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="7">
         <v>46128</v>
       </c>
@@ -11016,7 +12926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="7">
         <v>46129</v>
       </c>
@@ -11033,7 +12943,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="7">
         <v>46130</v>
       </c>
@@ -11050,7 +12960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="7">
         <v>46131</v>
       </c>
@@ -11067,7 +12977,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="7">
         <v>46132</v>
       </c>
@@ -11084,7 +12994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="7">
         <v>46133</v>
       </c>
@@ -11101,7 +13011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="7">
         <v>46134</v>
       </c>
@@ -11118,7 +13028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="7">
         <v>46135</v>
       </c>
@@ -11135,7 +13045,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="7">
         <v>46136</v>
       </c>
@@ -11152,7 +13062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="7">
         <v>46137</v>
       </c>
@@ -11169,7 +13079,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="7">
         <v>46138</v>
       </c>
@@ -11186,7 +13096,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="7">
         <v>46139</v>
       </c>
@@ -11203,7 +13113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="7">
         <v>46140</v>
       </c>
@@ -11220,7 +13130,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="7">
         <v>46141</v>
       </c>
@@ -11237,7 +13147,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="7">
         <v>46142</v>
       </c>
@@ -11254,7 +13164,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="7">
         <v>46143</v>
       </c>
@@ -11271,7 +13181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="7">
         <v>46144</v>
       </c>
@@ -11288,7 +13198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="7">
         <v>46145</v>
       </c>
@@ -11305,7 +13215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="7">
         <v>46146</v>
       </c>
@@ -11322,7 +13232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="7">
         <v>46147</v>
       </c>
@@ -11339,7 +13249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="7">
         <v>46148</v>
       </c>
@@ -11356,7 +13266,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="7">
         <v>46149</v>
       </c>
@@ -11373,7 +13283,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="7">
         <v>46150</v>
       </c>
@@ -11390,7 +13300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="7">
         <v>46151</v>
       </c>
@@ -11407,7 +13317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="7">
         <v>46152</v>
       </c>
@@ -11424,7 +13334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="7">
         <v>46153</v>
       </c>
@@ -11441,7 +13351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="7">
         <v>46154</v>
       </c>
@@ -11458,7 +13368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="7">
         <v>46155</v>
       </c>
@@ -11475,7 +13385,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="7">
         <v>46156</v>
       </c>
@@ -11492,7 +13402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="7">
         <v>46157</v>
       </c>
@@ -11509,7 +13419,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="7">
         <v>46158</v>
       </c>
@@ -11526,7 +13436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="7">
         <v>46160</v>
       </c>
@@ -11543,7 +13453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="7">
         <v>46161</v>
       </c>
@@ -11560,7 +13470,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="7">
         <v>46162</v>
       </c>
@@ -11577,7 +13487,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" s="7">
         <v>46163</v>
       </c>
@@ -11594,7 +13504,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="7">
         <v>46164</v>
       </c>
@@ -11611,7 +13521,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="7">
         <v>46166</v>
       </c>
@@ -11628,7 +13538,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="7">
         <v>46167</v>
       </c>
@@ -11645,7 +13555,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="7">
         <v>46168</v>
       </c>
@@ -11662,7 +13572,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="7">
         <v>46169</v>
       </c>
@@ -11679,7 +13589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="7">
         <v>46170</v>
       </c>
@@ -11696,7 +13606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="7">
         <v>46171</v>
       </c>
@@ -11713,7 +13623,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="7">
         <v>46173</v>
       </c>
@@ -11730,7 +13640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="7">
         <v>46174</v>
       </c>
@@ -11747,7 +13657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="7">
         <v>46175</v>
       </c>
@@ -11764,7 +13674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="7">
         <v>46176</v>
       </c>
@@ -11781,7 +13691,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="7">
         <v>46177</v>
       </c>
@@ -11798,7 +13708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="7">
         <v>46178</v>
       </c>
@@ -11815,7 +13725,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="7">
         <v>46179</v>
       </c>
@@ -11832,7 +13742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="7">
         <v>46180</v>
       </c>
@@ -11849,7 +13759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="7">
         <v>46181</v>
       </c>
@@ -11866,7 +13776,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="7">
         <v>46182</v>
       </c>
@@ -11883,7 +13793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="7">
         <v>46183</v>
       </c>
@@ -11900,7 +13810,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="7">
         <v>46184</v>
       </c>
@@ -11917,7 +13827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="7">
         <v>46185</v>
       </c>
@@ -11934,7 +13844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="7">
         <v>46186</v>
       </c>
@@ -11951,7 +13861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="7">
         <v>46187</v>
       </c>
@@ -11968,7 +13878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="7">
         <v>46188</v>
       </c>
@@ -11985,7 +13895,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="7">
         <v>46189</v>
       </c>
@@ -12002,7 +13912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="7">
         <v>46190</v>
       </c>
@@ -12019,7 +13929,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="7">
         <v>46191</v>
       </c>
@@ -12036,7 +13946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="7">
         <v>46192</v>
       </c>
@@ -12053,7 +13963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="7">
         <v>46193</v>
       </c>
@@ -12070,7 +13980,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="7">
         <v>46194</v>
       </c>
@@ -12087,7 +13997,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="7">
         <v>46195</v>
       </c>
@@ -12104,7 +14014,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="7">
         <v>46196</v>
       </c>
@@ -12121,7 +14031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>987</v>
       </c>
@@ -12142,15 +14052,15 @@
         <v>2666</v>
       </c>
     </row>
-    <row r="227" spans="1:6" ht="16" x14ac:dyDescent="0.4">
-      <c r="A227" s="12" t="s">
+    <row r="227" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A227" s="13" t="s">
         <v>989</v>
       </c>
-      <c r="B227" s="12"/>
-      <c r="C227" s="12"/>
-      <c r="D227" s="12"/>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="B227" s="13"/>
+      <c r="C227" s="13"/>
+      <c r="D227" s="13"/>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="9"/>
       <c r="B228" s="9"/>
       <c r="C228" s="9"/>
@@ -12159,7 +14069,7 @@
       </c>
       <c r="E228" s="9"/>
     </row>
-    <row r="229" spans="1:6" ht="16" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
         <v>126</v>
       </c>
@@ -12179,8 +14089,8 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="230" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A230" s="13" t="s">
+    <row r="230" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A230" s="11" t="s">
         <v>212</v>
       </c>
       <c r="B230" s="10" t="s">
@@ -12189,623 +14099,670 @@
       <c r="C230" s="10" t="s">
         <v>1232</v>
       </c>
-      <c r="D230" s="11">
+      <c r="D230" s="16">
         <v>13</v>
       </c>
-      <c r="E230" s="2">
+      <c r="E230" s="17">
         <v>11</v>
       </c>
       <c r="F230" s="6">
-        <f>E230/D230</f>
+        <f t="shared" ref="F230:F264" si="0">E230/D230</f>
         <v>0.84615384615384615</v>
       </c>
     </row>
-    <row r="231" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A231" s="14"/>
-      <c r="B231" s="15" t="s">
+    <row r="231" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A231" s="12"/>
+      <c r="B231" s="14" t="s">
         <v>273</v>
       </c>
       <c r="C231" s="10" t="s">
         <v>1233</v>
       </c>
-      <c r="D231" s="11">
+      <c r="D231" s="16">
         <v>7</v>
       </c>
-      <c r="E231" s="2">
+      <c r="E231" s="17">
         <v>6</v>
       </c>
       <c r="F231" s="6">
-        <f>E231/D231</f>
+        <f t="shared" si="0"/>
         <v>0.8571428571428571</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A232" s="14"/>
-      <c r="B232" s="16" t="s">
+    <row r="232" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A232" s="12"/>
+      <c r="B232" s="15" t="s">
         <v>273</v>
       </c>
       <c r="C232" s="10" t="s">
         <v>1234</v>
       </c>
-      <c r="D232" s="11">
+      <c r="D232" s="16">
         <v>6</v>
       </c>
-      <c r="E232" s="2">
+      <c r="E232" s="17">
         <v>6</v>
       </c>
       <c r="F232" s="6">
-        <f>E232/D232</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A233" s="14"/>
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A233" s="12"/>
       <c r="B233" s="10" t="s">
         <v>477</v>
       </c>
       <c r="C233" s="10" t="s">
         <v>1221</v>
       </c>
-      <c r="D233" s="11">
+      <c r="D233" s="16">
         <v>10</v>
       </c>
-      <c r="E233" s="2">
+      <c r="E233" s="17">
         <v>9</v>
       </c>
       <c r="F233" s="6">
-        <f>E233/D233</f>
+        <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
     </row>
-    <row r="234" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A234" s="14"/>
+    <row r="234" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A234" s="12"/>
       <c r="B234" s="10" t="s">
         <v>377</v>
       </c>
       <c r="C234" s="10" t="s">
         <v>1218</v>
       </c>
-      <c r="D234" s="11">
+      <c r="D234" s="16">
         <v>8</v>
       </c>
-      <c r="E234" s="2">
+      <c r="E234" s="17">
         <v>5</v>
       </c>
       <c r="F234" s="6">
-        <f>E234/D234</f>
+        <f t="shared" si="0"/>
         <v>0.625</v>
       </c>
     </row>
-    <row r="235" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A235" s="14"/>
+    <row r="235" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A235" s="12"/>
       <c r="B235" s="10" t="s">
         <v>387</v>
       </c>
       <c r="C235" s="10" t="s">
         <v>1220</v>
       </c>
-      <c r="D235" s="11">
+      <c r="D235" s="16">
         <v>5</v>
       </c>
-      <c r="E235" s="2">
+      <c r="E235" s="17">
         <v>5</v>
       </c>
       <c r="F235" s="6">
-        <f>E235/D235</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A236" s="14"/>
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A236" s="12"/>
       <c r="B236" s="10" t="s">
         <v>1080</v>
       </c>
       <c r="C236" s="10" t="s">
         <v>1219</v>
       </c>
-      <c r="D236" s="11">
+      <c r="D236" s="16">
         <v>3</v>
       </c>
-      <c r="E236" s="2">
+      <c r="E236" s="17">
         <v>2</v>
       </c>
       <c r="F236" s="6">
-        <f>E236/D236</f>
+        <f t="shared" si="0"/>
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="237" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A237" s="13" t="s">
+    <row r="237" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A237" s="12"/>
+      <c r="B237" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="C237" s="8" t="s">
+        <v>1219</v>
+      </c>
+      <c r="D237" s="16">
+        <v>1</v>
+      </c>
+      <c r="E237" s="17">
+        <v>0</v>
+      </c>
+      <c r="F237" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A238" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B237" s="10" t="s">
+      <c r="B238" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="C237" s="10" t="s">
+      <c r="C238" s="10" t="s">
         <v>1222</v>
       </c>
-      <c r="D237" s="11">
+      <c r="D238" s="16">
         <v>12</v>
       </c>
-      <c r="E237" s="2">
+      <c r="E238" s="17">
         <v>7</v>
       </c>
-      <c r="F237" s="6">
-        <f>E237/D237</f>
+      <c r="F238" s="6">
+        <f t="shared" si="0"/>
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="238" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A238" s="14"/>
-      <c r="B238" s="10" t="s">
+    <row r="239" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A239" s="12"/>
+      <c r="B239" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C238" s="10" t="s">
+      <c r="C239" s="10" t="s">
         <v>1235</v>
       </c>
-      <c r="D238" s="11">
+      <c r="D239" s="16">
         <v>12</v>
       </c>
-      <c r="E238" s="2">
+      <c r="E239" s="17">
         <v>9</v>
       </c>
-      <c r="F238" s="6">
-        <f>E238/D238</f>
+      <c r="F239" s="6">
+        <f t="shared" si="0"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A239" s="14"/>
-      <c r="B239" s="10" t="s">
+    <row r="240" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A240" s="12"/>
+      <c r="B240" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C239" s="10" t="s">
+      <c r="C240" s="10" t="s">
         <v>1229</v>
       </c>
-      <c r="D239" s="11">
+      <c r="D240" s="16">
         <v>12</v>
       </c>
-      <c r="E239" s="2">
+      <c r="E240" s="17">
         <v>11</v>
       </c>
-      <c r="F239" s="6">
-        <f>E239/D239</f>
+      <c r="F240" s="6">
+        <f t="shared" si="0"/>
         <v>0.91666666666666663</v>
       </c>
     </row>
-    <row r="240" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A240" s="14"/>
-      <c r="B240" s="10" t="s">
+    <row r="241" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A241" s="12"/>
+      <c r="B241" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="C240" s="10" t="s">
+      <c r="C241" s="10" t="s">
         <v>1236</v>
       </c>
-      <c r="D240" s="11">
+      <c r="D241" s="16">
         <v>7</v>
       </c>
-      <c r="E240" s="2">
+      <c r="E241" s="17">
         <v>7</v>
       </c>
-      <c r="F240" s="6">
-        <f>E240/D240</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A241" s="14"/>
-      <c r="B241" s="15" t="s">
+      <c r="F241" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A242" s="12"/>
+      <c r="B242" s="14" t="s">
         <v>331</v>
       </c>
-      <c r="C241" s="10" t="s">
+      <c r="C242" s="10" t="s">
         <v>1231</v>
       </c>
-      <c r="D241" s="11">
+      <c r="D242" s="16">
         <v>3</v>
       </c>
-      <c r="E241" s="2">
+      <c r="E242" s="17">
         <v>3</v>
       </c>
-      <c r="F241" s="6">
-        <f>E241/D241</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A242" s="14"/>
-      <c r="B242" s="16" t="s">
+      <c r="F242" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A243" s="12"/>
+      <c r="B243" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="C242" s="10" t="s">
+      <c r="C243" s="10" t="s">
         <v>1230</v>
       </c>
-      <c r="D242" s="11">
+      <c r="D243" s="16">
         <v>3</v>
       </c>
-      <c r="E242" s="2">
-        <v>1</v>
-      </c>
-      <c r="F242" s="6">
-        <f>E242/D242</f>
+      <c r="E243" s="17">
+        <v>1</v>
+      </c>
+      <c r="F243" s="6">
+        <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="243" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A243" s="14"/>
-      <c r="B243" s="10" t="s">
+    <row r="244" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A244" s="12"/>
+      <c r="B244" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="C243" s="10" t="s">
+      <c r="C244" s="10" t="s">
         <v>1227</v>
       </c>
-      <c r="D243" s="11">
+      <c r="D244" s="16">
         <v>3</v>
       </c>
-      <c r="E243" s="2">
+      <c r="E244" s="17">
         <v>3</v>
       </c>
-      <c r="F243" s="6">
-        <f>E243/D243</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A244" s="14"/>
-      <c r="B244" s="10" t="s">
+      <c r="F244" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A245" s="12"/>
+      <c r="B245" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="C244" s="10" t="s">
+      <c r="C245" s="10" t="s">
         <v>1228</v>
       </c>
-      <c r="D244" s="11">
+      <c r="D245" s="16">
         <v>3</v>
       </c>
-      <c r="E244" s="2">
-        <v>1</v>
-      </c>
-      <c r="F244" s="6">
-        <f>E244/D244</f>
+      <c r="E245" s="17">
+        <v>1</v>
+      </c>
+      <c r="F245" s="6">
+        <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="245" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A245" s="14"/>
-      <c r="B245" s="10" t="s">
+    <row r="246" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A246" s="12"/>
+      <c r="B246" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="C245" s="10" t="s">
+      <c r="C246" s="10" t="s">
         <v>1227</v>
       </c>
-      <c r="D245" s="11">
+      <c r="D246" s="16">
         <v>2</v>
       </c>
-      <c r="E245" s="2">
-        <v>1</v>
-      </c>
-      <c r="F245" s="6">
-        <f>E245/D245</f>
+      <c r="E246" s="17">
+        <v>1</v>
+      </c>
+      <c r="F246" s="6">
+        <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="246" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A246" s="13" t="s">
+    <row r="247" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A247" s="12"/>
+      <c r="B247" s="10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C247" s="8" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D247" s="16">
+        <v>1</v>
+      </c>
+      <c r="E247" s="17">
+        <v>1</v>
+      </c>
+      <c r="F247" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A248" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B246" s="10" t="s">
+      <c r="B248" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C246" s="10" t="s">
+      <c r="C248" s="10" t="s">
         <v>1239</v>
       </c>
-      <c r="D246" s="11">
+      <c r="D248" s="16">
         <v>32</v>
       </c>
-      <c r="E246" s="2">
+      <c r="E248" s="17">
         <v>25</v>
       </c>
-      <c r="F246" s="6">
-        <f>E246/D246</f>
+      <c r="F248" s="6">
+        <f t="shared" si="0"/>
         <v>0.78125</v>
       </c>
     </row>
-    <row r="247" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A247" s="14"/>
-      <c r="B247" s="10" t="s">
+    <row r="249" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A249" s="12"/>
+      <c r="B249" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C247" s="10" t="s">
+      <c r="C249" s="10" t="s">
         <v>1226</v>
       </c>
-      <c r="D247" s="11">
+      <c r="D249" s="16">
         <v>26</v>
       </c>
-      <c r="E247" s="2">
+      <c r="E249" s="17">
         <v>18</v>
       </c>
-      <c r="F247" s="6">
-        <f>E247/D247</f>
+      <c r="F249" s="6">
+        <f t="shared" si="0"/>
         <v>0.69230769230769229</v>
       </c>
     </row>
-    <row r="248" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A248" s="14"/>
-      <c r="B248" s="10" t="s">
+    <row r="250" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A250" s="12"/>
+      <c r="B250" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="C248" s="10" t="s">
+      <c r="C250" s="10" t="s">
         <v>1238</v>
       </c>
-      <c r="D248" s="11">
+      <c r="D250" s="16">
         <v>19</v>
       </c>
-      <c r="E248" s="2">
+      <c r="E250" s="17">
         <v>16</v>
       </c>
-      <c r="F248" s="6">
-        <f>E248/D248</f>
+      <c r="F250" s="6">
+        <f t="shared" si="0"/>
         <v>0.84210526315789469</v>
       </c>
     </row>
-    <row r="249" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A249" s="14"/>
-      <c r="B249" s="10" t="s">
+    <row r="251" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A251" s="12"/>
+      <c r="B251" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C251" s="10" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D251" s="16">
+        <v>17</v>
+      </c>
+      <c r="E251" s="17">
+        <v>12</v>
+      </c>
+      <c r="F251" s="6">
+        <f t="shared" si="0"/>
+        <v>0.70588235294117652</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A252" s="12"/>
+      <c r="B252" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="C249" s="10" t="s">
+      <c r="C252" s="10" t="s">
         <v>1223</v>
       </c>
-      <c r="D249" s="11">
+      <c r="D252" s="16">
         <v>17</v>
       </c>
-      <c r="E249" s="2">
+      <c r="E252" s="17">
         <v>11</v>
       </c>
-      <c r="F249" s="6">
-        <f>E249/D249</f>
+      <c r="F252" s="6">
+        <f t="shared" si="0"/>
         <v>0.6470588235294118</v>
       </c>
     </row>
-    <row r="250" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A250" s="14"/>
-      <c r="B250" s="10" t="s">
-        <v>194</v>
-      </c>
-      <c r="C250" s="10" t="s">
+    <row r="253" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A253" s="12"/>
+      <c r="B253" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="C253" s="10" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D253" s="16">
+        <v>12</v>
+      </c>
+      <c r="E253" s="17">
+        <v>11</v>
+      </c>
+      <c r="F253" s="6">
+        <f t="shared" si="0"/>
+        <v>0.91666666666666663</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A254" s="12"/>
+      <c r="B254" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="C254" s="10" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D254" s="16">
+        <v>11</v>
+      </c>
+      <c r="E254" s="17">
+        <v>9</v>
+      </c>
+      <c r="F254" s="6">
+        <f t="shared" si="0"/>
+        <v>0.81818181818181823</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A255" s="12"/>
+      <c r="B255" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C255" s="10" t="s">
         <v>1224</v>
       </c>
-      <c r="D250" s="11">
-        <v>17</v>
-      </c>
-      <c r="E250" s="2">
-        <v>12</v>
-      </c>
-      <c r="F250" s="6">
-        <f>E250/D250</f>
-        <v>0.70588235294117652</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A251" s="14"/>
-      <c r="B251" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C251" s="10" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D251" s="11">
-        <v>12</v>
-      </c>
-      <c r="E251" s="2">
+      <c r="D255" s="16">
+        <v>8</v>
+      </c>
+      <c r="E255" s="17">
+        <v>7</v>
+      </c>
+      <c r="F255" s="6">
+        <f t="shared" si="0"/>
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A256" s="12"/>
+      <c r="B256" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C256" s="10" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D256" s="16">
+        <v>7</v>
+      </c>
+      <c r="E256" s="17">
+        <v>6</v>
+      </c>
+      <c r="F256" s="6">
+        <f t="shared" si="0"/>
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A257" s="12"/>
+      <c r="B257" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="C257" s="10" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D257" s="16">
+        <v>6</v>
+      </c>
+      <c r="E257" s="17">
+        <v>4</v>
+      </c>
+      <c r="F257" s="6">
+        <f t="shared" si="0"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A258" s="12"/>
+      <c r="B258" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="C258" s="10" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D258" s="16">
+        <v>4</v>
+      </c>
+      <c r="E258" s="17">
+        <v>2</v>
+      </c>
+      <c r="F258" s="6">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A259" s="12"/>
+      <c r="B259" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="C259" s="8" t="s">
+        <v>1684</v>
+      </c>
+      <c r="D259" s="16">
+        <v>1</v>
+      </c>
+      <c r="E259" s="17">
+        <v>0</v>
+      </c>
+      <c r="F259" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A260" s="12"/>
+      <c r="B260" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="C260" s="8" t="s">
+        <v>1238</v>
+      </c>
+      <c r="D260" s="16">
+        <v>4</v>
+      </c>
+      <c r="E260" s="17">
+        <v>3</v>
+      </c>
+      <c r="F260" s="6">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A261" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B261" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C261" s="10" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D261" s="16">
+        <v>13</v>
+      </c>
+      <c r="E261" s="17">
         <v>11</v>
       </c>
-      <c r="F251" s="6">
-        <f>E251/D251</f>
-        <v>0.91666666666666663</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A252" s="14"/>
-      <c r="B252" s="10" t="s">
-        <v>409</v>
-      </c>
-      <c r="C252" s="10" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D252" s="11">
-        <v>11</v>
-      </c>
-      <c r="E252" s="2">
-        <v>9</v>
-      </c>
-      <c r="F252" s="6">
-        <f>E252/D252</f>
-        <v>0.81818181818181823</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A253" s="14"/>
-      <c r="B253" s="10" t="s">
-        <v>254</v>
-      </c>
-      <c r="C253" s="10" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D253" s="11">
-        <v>8</v>
-      </c>
-      <c r="E253" s="2">
-        <v>7</v>
-      </c>
-      <c r="F253" s="6">
-        <f>E253/D253</f>
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A254" s="14"/>
-      <c r="B254" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="C254" s="10" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D254" s="11">
-        <v>7</v>
-      </c>
-      <c r="E254" s="2">
-        <v>6</v>
-      </c>
-      <c r="F254" s="6">
-        <f>E254/D254</f>
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A255" s="14"/>
-      <c r="B255" s="10" t="s">
-        <v>498</v>
-      </c>
-      <c r="C255" s="10" t="s">
-        <v>1223</v>
-      </c>
-      <c r="D255" s="11">
-        <v>6</v>
-      </c>
-      <c r="E255" s="2">
-        <v>4</v>
-      </c>
-      <c r="F255" s="6">
-        <f>E255/D255</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A256" s="14"/>
-      <c r="B256" s="15" t="s">
-        <v>610</v>
-      </c>
-      <c r="C256" s="10" t="s">
-        <v>1242</v>
-      </c>
-      <c r="D256" s="11">
-        <v>4</v>
-      </c>
-      <c r="E256" s="2">
+      <c r="F261" s="6">
+        <f t="shared" si="0"/>
+        <v>0.84615384615384615</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A262" s="12"/>
+      <c r="B262" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C262" s="10" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D262" s="16">
         <v>2</v>
       </c>
-      <c r="F256" s="6">
-        <f>E256/D256</f>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A257" s="14"/>
-      <c r="B257" s="16" t="s">
-        <v>610</v>
-      </c>
-      <c r="C257" s="8" t="s">
-        <v>1684</v>
-      </c>
-      <c r="D257" s="11">
-        <v>1</v>
-      </c>
-      <c r="E257" s="2">
-        <v>0</v>
-      </c>
-      <c r="F257" s="6">
-        <f>E257/D257</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A258" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="B258" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C258" s="10" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D258" s="11">
-        <v>13</v>
-      </c>
-      <c r="E258" s="2">
-        <v>11</v>
-      </c>
-      <c r="F258" s="6">
-        <f>E258/D258</f>
-        <v>0.84615384615384615</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A259" s="14"/>
-      <c r="B259" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="C259" s="10" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D259" s="11">
+      <c r="E262" s="17">
         <v>2</v>
       </c>
-      <c r="E259" s="2">
-        <v>2</v>
-      </c>
-      <c r="F259" s="6">
-        <f>E259/D259</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A260" s="13" t="s">
+      <c r="F262" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A263" s="11" t="s">
         <v>990</v>
       </c>
-      <c r="B260" s="14"/>
-      <c r="C260" s="14"/>
-      <c r="D260" s="2">
-        <v>282</v>
-      </c>
-      <c r="E260" s="2">
-        <v>221</v>
-      </c>
-      <c r="F260" s="6">
-        <f>E260/D260</f>
-        <v>0.78368794326241131</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A261"/>
-      <c r="B261"/>
-      <c r="C261"/>
-      <c r="D261"/>
-      <c r="E261"/>
-    </row>
-    <row r="262" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A262"/>
-      <c r="B262"/>
-      <c r="C262"/>
-      <c r="D262"/>
-      <c r="E262"/>
-    </row>
-    <row r="263" spans="1:6" ht="17" x14ac:dyDescent="0.4">
-      <c r="A263"/>
-      <c r="B263"/>
-      <c r="C263"/>
-      <c r="D263"/>
-      <c r="E263"/>
+      <c r="B263" s="12"/>
+      <c r="C263" s="12"/>
+      <c r="D263" s="17">
+        <v>288</v>
+      </c>
+      <c r="E263" s="17">
+        <v>225</v>
+      </c>
+      <c r="F263" s="6">
+        <f t="shared" si="0"/>
+        <v>0.78125</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A264"/>
+      <c r="B264"/>
+      <c r="C264"/>
+      <c r="D264"/>
+      <c r="E264"/>
+      <c r="F264" s="6" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A260:C260"/>
+    <mergeCell ref="A230:A237"/>
+    <mergeCell ref="A238:A247"/>
+    <mergeCell ref="A248:A260"/>
+    <mergeCell ref="A261:A262"/>
+    <mergeCell ref="A263:C263"/>
+    <mergeCell ref="B231:B232"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B258:B259"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A230:A236"/>
-    <mergeCell ref="A237:A245"/>
-    <mergeCell ref="A246:A257"/>
-    <mergeCell ref="A258:A259"/>
-    <mergeCell ref="B231:B232"/>
-    <mergeCell ref="B241:B242"/>
-    <mergeCell ref="B256:B257"/>
     <mergeCell ref="A227:D227"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12820,26 +14777,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S292"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.25" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="23" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="7.5" bestFit="1" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>126</v>
       </c>
@@ -12898,7 +14855,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>212</v>
       </c>
@@ -12957,7 +14914,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>149</v>
       </c>
@@ -13016,7 +14973,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>149</v>
       </c>
@@ -13075,7 +15032,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>149</v>
       </c>
@@ -13134,7 +15091,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>149</v>
       </c>
@@ -13193,7 +15150,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>149</v>
       </c>
@@ -13252,7 +15209,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>212</v>
       </c>
@@ -13311,7 +15268,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>149</v>
       </c>
@@ -13370,7 +15327,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>141</v>
       </c>
@@ -13429,7 +15386,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>212</v>
       </c>
@@ -13488,7 +15445,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>178</v>
       </c>
@@ -13547,7 +15504,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>178</v>
       </c>
@@ -13606,7 +15563,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>212</v>
       </c>
@@ -13665,7 +15622,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>149</v>
       </c>
@@ -13724,7 +15681,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>141</v>
       </c>
@@ -13783,7 +15740,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>212</v>
       </c>
@@ -13842,7 +15799,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>149</v>
       </c>
@@ -13901,7 +15858,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>212</v>
       </c>
@@ -13960,7 +15917,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>178</v>
       </c>
@@ -14019,7 +15976,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>149</v>
       </c>
@@ -14078,7 +16035,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>212</v>
       </c>
@@ -14137,7 +16094,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>149</v>
       </c>
@@ -14196,7 +16153,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>149</v>
       </c>
@@ -14255,7 +16212,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>149</v>
       </c>
@@ -14314,7 +16271,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>149</v>
       </c>
@@ -14373,7 +16330,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>149</v>
       </c>
@@ -14432,7 +16389,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>149</v>
       </c>
@@ -14491,7 +16448,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>212</v>
       </c>
@@ -14550,7 +16507,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>149</v>
       </c>
@@ -14609,7 +16566,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>149</v>
       </c>
@@ -14668,7 +16625,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>149</v>
       </c>
@@ -14727,7 +16684,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>149</v>
       </c>
@@ -14786,7 +16743,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>149</v>
       </c>
@@ -14845,7 +16802,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>212</v>
       </c>
@@ -14904,7 +16861,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>212</v>
       </c>
@@ -14963,7 +16920,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>212</v>
       </c>
@@ -15022,7 +16979,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>141</v>
       </c>
@@ -15081,7 +17038,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>149</v>
       </c>
@@ -15140,7 +17097,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>149</v>
       </c>
@@ -15199,7 +17156,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>149</v>
       </c>
@@ -15258,7 +17215,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>149</v>
       </c>
@@ -15317,7 +17274,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>178</v>
       </c>
@@ -15376,7 +17333,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>178</v>
       </c>
@@ -15435,7 +17392,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>149</v>
       </c>
@@ -15494,7 +17451,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>178</v>
       </c>
@@ -15553,7 +17510,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>178</v>
       </c>
@@ -15612,7 +17569,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>149</v>
       </c>
@@ -15671,7 +17628,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>212</v>
       </c>
@@ -15730,7 +17687,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>178</v>
       </c>
@@ -15789,7 +17746,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>149</v>
       </c>
@@ -15848,7 +17805,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>149</v>
       </c>
@@ -15907,7 +17864,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>178</v>
       </c>
@@ -15966,7 +17923,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>149</v>
       </c>
@@ -16025,7 +17982,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>149</v>
       </c>
@@ -16084,7 +18041,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>178</v>
       </c>
@@ -16143,7 +18100,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>149</v>
       </c>
@@ -16202,7 +18159,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>178</v>
       </c>
@@ -16261,7 +18218,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>141</v>
       </c>
@@ -16320,7 +18277,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>141</v>
       </c>
@@ -16379,7 +18336,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>149</v>
       </c>
@@ -16438,7 +18395,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>212</v>
       </c>
@@ -16497,7 +18454,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>178</v>
       </c>
@@ -16556,7 +18513,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>149</v>
       </c>
@@ -16615,7 +18572,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>149</v>
       </c>
@@ -16674,7 +18631,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>149</v>
       </c>
@@ -16733,7 +18690,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>212</v>
       </c>
@@ -16792,7 +18749,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>178</v>
       </c>
@@ -16851,7 +18808,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>149</v>
       </c>
@@ -16910,7 +18867,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>149</v>
       </c>
@@ -16969,7 +18926,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>149</v>
       </c>
@@ -17028,7 +18985,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>178</v>
       </c>
@@ -17087,7 +19044,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>149</v>
       </c>
@@ -17146,7 +19103,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>149</v>
       </c>
@@ -17205,7 +19162,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>212</v>
       </c>
@@ -17264,7 +19221,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>149</v>
       </c>
@@ -17323,7 +19280,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>149</v>
       </c>
@@ -17382,7 +19339,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>149</v>
       </c>
@@ -17441,7 +19398,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>212</v>
       </c>
@@ -17500,7 +19457,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>149</v>
       </c>
@@ -17559,7 +19516,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>212</v>
       </c>
@@ -17618,7 +19575,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>178</v>
       </c>
@@ -17677,7 +19634,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>149</v>
       </c>
@@ -17736,7 +19693,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>149</v>
       </c>
@@ -17795,7 +19752,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>149</v>
       </c>
@@ -17854,7 +19811,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>141</v>
       </c>
@@ -17913,7 +19870,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>149</v>
       </c>
@@ -17972,7 +19929,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>149</v>
       </c>
@@ -18031,7 +19988,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>149</v>
       </c>
@@ -18090,7 +20047,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>149</v>
       </c>
@@ -18149,7 +20106,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>178</v>
       </c>
@@ -18208,7 +20165,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>149</v>
       </c>
@@ -18267,7 +20224,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>141</v>
       </c>
@@ -18326,7 +20283,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>149</v>
       </c>
@@ -18385,7 +20342,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>141</v>
       </c>
@@ -18444,7 +20401,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>178</v>
       </c>
@@ -18503,7 +20460,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>149</v>
       </c>
@@ -18562,7 +20519,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>212</v>
       </c>
@@ -18621,7 +20578,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>178</v>
       </c>
@@ -18680,7 +20637,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>178</v>
       </c>
@@ -18739,7 +20696,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>149</v>
       </c>
@@ -18798,7 +20755,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>149</v>
       </c>
@@ -18857,7 +20814,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>149</v>
       </c>
@@ -18916,7 +20873,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>149</v>
       </c>
@@ -18975,7 +20932,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>149</v>
       </c>
@@ -19034,7 +20991,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>178</v>
       </c>
@@ -19093,7 +21050,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>212</v>
       </c>
@@ -19152,7 +21109,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>178</v>
       </c>
@@ -19211,7 +21168,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>149</v>
       </c>
@@ -19270,7 +21227,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>212</v>
       </c>
@@ -19329,7 +21286,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>141</v>
       </c>
@@ -19388,7 +21345,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>178</v>
       </c>
@@ -19447,7 +21404,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>212</v>
       </c>
@@ -19506,7 +21463,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>149</v>
       </c>
@@ -19565,7 +21522,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>141</v>
       </c>
@@ -19624,7 +21581,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>149</v>
       </c>
@@ -19683,7 +21640,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>149</v>
       </c>
@@ -19742,7 +21699,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>212</v>
       </c>
@@ -19801,7 +21758,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>212</v>
       </c>
@@ -19860,7 +21817,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>149</v>
       </c>
@@ -19919,7 +21876,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>178</v>
       </c>
@@ -19978,7 +21935,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>149</v>
       </c>
@@ -20037,7 +21994,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>149</v>
       </c>
@@ -20096,7 +22053,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>178</v>
       </c>
@@ -20155,7 +22112,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>149</v>
       </c>
@@ -20214,7 +22171,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>149</v>
       </c>
@@ -20273,7 +22230,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>212</v>
       </c>
@@ -20332,7 +22289,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>212</v>
       </c>
@@ -20391,7 +22348,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>178</v>
       </c>
@@ -20450,7 +22407,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>149</v>
       </c>
@@ -20509,7 +22466,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>212</v>
       </c>
@@ -20568,7 +22525,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>212</v>
       </c>
@@ -20627,7 +22584,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>178</v>
       </c>
@@ -20686,7 +22643,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>149</v>
       </c>
@@ -20745,7 +22702,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>149</v>
       </c>
@@ -20804,7 +22761,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>149</v>
       </c>
@@ -20863,7 +22820,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>149</v>
       </c>
@@ -20922,7 +22879,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>149</v>
       </c>
@@ -20981,7 +22938,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>149</v>
       </c>
@@ -21040,7 +22997,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>149</v>
       </c>
@@ -21099,7 +23056,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>149</v>
       </c>
@@ -21158,7 +23115,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>149</v>
       </c>
@@ -21217,7 +23174,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>178</v>
       </c>
@@ -21276,7 +23233,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>149</v>
       </c>
@@ -21335,7 +23292,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>178</v>
       </c>
@@ -21394,7 +23351,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>178</v>
       </c>
@@ -21453,7 +23410,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>149</v>
       </c>
@@ -21512,7 +23469,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>149</v>
       </c>
@@ -21571,7 +23528,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>149</v>
       </c>
@@ -21630,7 +23587,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>149</v>
       </c>
@@ -21689,7 +23646,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>141</v>
       </c>
@@ -21748,7 +23705,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>149</v>
       </c>
@@ -21807,7 +23764,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>149</v>
       </c>
@@ -21866,7 +23823,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>149</v>
       </c>
@@ -21925,7 +23882,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>149</v>
       </c>
@@ -21984,7 +23941,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>178</v>
       </c>
@@ -22043,7 +24000,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>178</v>
       </c>
@@ -22102,7 +24059,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>149</v>
       </c>
@@ -22161,7 +24118,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>178</v>
       </c>
@@ -22220,7 +24177,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>178</v>
       </c>
@@ -22279,7 +24236,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>149</v>
       </c>
@@ -22338,7 +24295,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>212</v>
       </c>
@@ -22397,7 +24354,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>149</v>
       </c>
@@ -22456,7 +24413,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>149</v>
       </c>
@@ -22515,7 +24472,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>149</v>
       </c>
@@ -22574,7 +24531,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>149</v>
       </c>
@@ -22633,7 +24590,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>149</v>
       </c>
@@ -22692,7 +24649,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>149</v>
       </c>
@@ -22751,7 +24708,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>149</v>
       </c>
@@ -22810,7 +24767,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>178</v>
       </c>
@@ -22869,7 +24826,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>149</v>
       </c>
@@ -22928,7 +24885,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>149</v>
       </c>
@@ -22987,7 +24944,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>141</v>
       </c>
@@ -23046,7 +25003,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>149</v>
       </c>
@@ -23105,7 +25062,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>212</v>
       </c>
@@ -23164,7 +25121,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>149</v>
       </c>
@@ -23223,7 +25180,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>149</v>
       </c>
@@ -23282,7 +25239,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>178</v>
       </c>
@@ -23341,7 +25298,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>178</v>
       </c>
@@ -23400,7 +25357,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>212</v>
       </c>
@@ -23459,7 +25416,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>149</v>
       </c>
@@ -23518,7 +25475,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>141</v>
       </c>
@@ -23577,7 +25534,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>212</v>
       </c>
@@ -23636,7 +25593,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>178</v>
       </c>
@@ -23695,7 +25652,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>178</v>
       </c>
@@ -23754,7 +25711,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>178</v>
       </c>
@@ -23813,7 +25770,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>149</v>
       </c>
@@ -23872,7 +25829,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>212</v>
       </c>
@@ -23931,7 +25888,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>149</v>
       </c>
@@ -23990,7 +25947,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>178</v>
       </c>
@@ -24049,7 +26006,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>178</v>
       </c>
@@ -24108,7 +26065,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>178</v>
       </c>
@@ -24167,7 +26124,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>178</v>
       </c>
@@ -24226,7 +26183,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="194" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>149</v>
       </c>
@@ -24285,7 +26242,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="195" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>178</v>
       </c>
@@ -24344,7 +26301,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="196" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>149</v>
       </c>
@@ -24403,7 +26360,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="197" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>149</v>
       </c>
@@ -24462,7 +26419,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="198" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>149</v>
       </c>
@@ -24521,7 +26478,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="199" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>149</v>
       </c>
@@ -24580,7 +26537,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="200" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>149</v>
       </c>
@@ -24639,7 +26596,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="201" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>178</v>
       </c>
@@ -24698,7 +26655,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="202" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>178</v>
       </c>
@@ -24757,7 +26714,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="203" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>212</v>
       </c>
@@ -24816,7 +26773,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="204" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>212</v>
       </c>
@@ -24875,7 +26832,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="205" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>212</v>
       </c>
@@ -24934,7 +26891,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="206" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>149</v>
       </c>
@@ -24993,7 +26950,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="207" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>149</v>
       </c>
@@ -25052,7 +27009,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="208" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>212</v>
       </c>
@@ -25111,7 +27068,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="209" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>149</v>
       </c>
@@ -25170,7 +27127,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="210" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>178</v>
       </c>
@@ -25229,7 +27186,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="211" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>149</v>
       </c>
@@ -25288,7 +27245,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="212" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>149</v>
       </c>
@@ -25347,7 +27304,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="213" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>149</v>
       </c>
@@ -25406,7 +27363,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="214" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>212</v>
       </c>
@@ -25465,7 +27422,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="215" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>149</v>
       </c>
@@ -25524,7 +27481,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="216" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>178</v>
       </c>
@@ -25583,7 +27540,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="217" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>178</v>
       </c>
@@ -25642,7 +27599,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="218" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>149</v>
       </c>
@@ -25701,7 +27658,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="219" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>212</v>
       </c>
@@ -25760,7 +27717,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="220" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>178</v>
       </c>
@@ -25819,7 +27776,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="221" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>212</v>
       </c>
@@ -25878,7 +27835,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="222" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>212</v>
       </c>
@@ -25937,7 +27894,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="223" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>149</v>
       </c>
@@ -25996,7 +27953,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="224" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>149</v>
       </c>
@@ -26055,7 +28012,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="225" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>178</v>
       </c>
@@ -26114,7 +28071,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="226" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>178</v>
       </c>
@@ -26173,7 +28130,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="227" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>212</v>
       </c>
@@ -26232,7 +28189,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="228" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>212</v>
       </c>
@@ -26291,7 +28248,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="229" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>178</v>
       </c>
@@ -26350,7 +28307,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="230" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>212</v>
       </c>
@@ -26409,7 +28366,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="231" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>149</v>
       </c>
@@ -26468,7 +28425,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="232" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>149</v>
       </c>
@@ -26527,7 +28484,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="233" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>149</v>
       </c>
@@ -26586,7 +28543,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="234" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>212</v>
       </c>
@@ -26645,7 +28602,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="235" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>149</v>
       </c>
@@ -26704,7 +28661,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="236" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>149</v>
       </c>
@@ -26763,7 +28720,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="237" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>212</v>
       </c>
@@ -26822,7 +28779,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="238" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>149</v>
       </c>
@@ -26881,7 +28838,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="239" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>141</v>
       </c>
@@ -26940,7 +28897,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="240" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>149</v>
       </c>
@@ -26999,7 +28956,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="241" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>149</v>
       </c>
@@ -27058,7 +29015,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="242" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>178</v>
       </c>
@@ -27117,7 +29074,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="243" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>212</v>
       </c>
@@ -27176,7 +29133,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="244" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>149</v>
       </c>
@@ -27235,7 +29192,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="245" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>212</v>
       </c>
@@ -27294,7 +29251,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="246" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>149</v>
       </c>
@@ -27353,7 +29310,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="247" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>141</v>
       </c>
@@ -27412,7 +29369,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="248" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>178</v>
       </c>
@@ -27471,7 +29428,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="249" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>149</v>
       </c>
@@ -27530,7 +29487,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="250" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>178</v>
       </c>
@@ -27589,7 +29546,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="251" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>178</v>
       </c>
@@ -27648,7 +29605,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="252" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>149</v>
       </c>
@@ -27707,7 +29664,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="253" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>149</v>
       </c>
@@ -27766,7 +29723,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="254" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>149</v>
       </c>
@@ -27825,7 +29782,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="255" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>149</v>
       </c>
@@ -27884,7 +29841,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="256" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>212</v>
       </c>
@@ -27943,7 +29900,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="257" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>212</v>
       </c>
@@ -28002,7 +29959,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="258" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>149</v>
       </c>
@@ -28061,7 +30018,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="259" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>149</v>
       </c>
@@ -28120,7 +30077,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="260" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>149</v>
       </c>
@@ -28179,7 +30136,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="261" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>149</v>
       </c>
@@ -28238,7 +30195,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="262" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>149</v>
       </c>
@@ -28297,7 +30254,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="263" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>212</v>
       </c>
@@ -28356,7 +30313,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="264" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>149</v>
       </c>
@@ -28415,7 +30372,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="265" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>178</v>
       </c>
@@ -28474,7 +30431,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="266" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>149</v>
       </c>
@@ -28533,7 +30490,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="267" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>149</v>
       </c>
@@ -28592,7 +30549,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="268" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>149</v>
       </c>
@@ -28651,7 +30608,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="269" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>149</v>
       </c>
@@ -28710,7 +30667,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="270" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>149</v>
       </c>
@@ -28769,7 +30726,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="271" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>149</v>
       </c>
@@ -28828,7 +30785,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="272" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>149</v>
       </c>
@@ -28887,7 +30844,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="273" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>149</v>
       </c>
@@ -28946,7 +30903,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="274" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>212</v>
       </c>
@@ -29005,7 +30962,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="275" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>149</v>
       </c>
@@ -29064,7 +31021,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="276" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>149</v>
       </c>
@@ -29123,7 +31080,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="277" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>149</v>
       </c>
@@ -29182,7 +31139,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="278" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>149</v>
       </c>
@@ -29241,7 +31198,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="279" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>149</v>
       </c>
@@ -29300,7 +31257,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="280" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>149</v>
       </c>
@@ -29359,7 +31316,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="281" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>149</v>
       </c>
@@ -29418,7 +31375,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="282" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>149</v>
       </c>
@@ -29477,7 +31434,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="283" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>149</v>
       </c>
@@ -29536,7 +31493,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="284" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>212</v>
       </c>
@@ -29595,7 +31552,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="285" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>149</v>
       </c>
@@ -29654,7 +31611,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="286" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>149</v>
       </c>
@@ -29713,7 +31670,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="287" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>149</v>
       </c>
@@ -29772,7 +31729,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="288" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>149</v>
       </c>
@@ -29831,7 +31788,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="289" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>149</v>
       </c>
@@ -29890,7 +31847,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="290" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>212</v>
       </c>
@@ -29949,7 +31906,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="291" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>149</v>
       </c>
@@ -30008,7 +31965,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="292" spans="1:19" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>149</v>
       </c>
@@ -30068,6 +32025,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:S1" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
